--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7274EE9A-A66C-4429-B262-2AEF74E2F729}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D46BD1D1-6C98-43CE-8B22-795425092EC2}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -146,7 +146,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -484,7 +489,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>700342565</v>
+        <v>669100574</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -492,7 +497,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>649316209</v>
+        <v>681109868</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -500,7 +505,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>672471327</v>
+        <v>747820839</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -508,7 +513,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>655119232</v>
+        <v>739687246</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -516,7 +521,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>568703684</v>
+        <v>726843174</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -524,7 +529,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>617212281</v>
+        <v>725868883</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -532,7 +537,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>616054023</v>
+        <v>725868875</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -540,7 +545,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>613914146</v>
+        <v>724644400</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -548,7 +553,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>612811384</v>
+        <v>695292767</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -556,7 +561,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>610108254</v>
+        <v>670930340</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -564,7 +569,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>730746587</v>
+        <v>672168170</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -572,7 +577,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>722659194</v>
+        <v>658886597</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -580,7 +585,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>722116666</v>
+        <v>645870548</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -588,7 +593,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>753517527</v>
+        <v>650250081</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -596,7 +601,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>758593929</v>
+        <v>648791477</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -604,7 +609,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>758593911</v>
+        <v>646421960</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -615,7 +620,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>758305407</v>
+        <v>645278700</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -623,7 +628,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>758305399</v>
+        <v>640633966</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -631,7 +636,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>733145050</v>
+        <v>640393199</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -639,7 +644,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>627404241</v>
+        <v>639504061</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -647,7 +652,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>631445461</v>
+        <v>638567663</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -655,7 +660,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>636618328</v>
+        <v>626969145</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -663,7 +668,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>637748439</v>
+        <v>620524813</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -671,7 +676,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>640607358</v>
+        <v>593551272</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -679,7 +684,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>640416172</v>
+        <v>759646619</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -687,7 +692,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>635994621</v>
+        <v>755265901</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -695,7 +700,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>628454617</v>
+        <v>759572484</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -703,7 +708,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>626460087</v>
+        <v>757556034</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -711,7 +716,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>622447666</v>
+        <v>757138585</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>2</v>
@@ -719,7 +724,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>619259314</v>
+        <v>754586513</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -727,7 +732,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>618350932</v>
+        <v>618972263</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -735,7 +740,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>563396609</v>
+        <v>618380608</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
@@ -743,7 +748,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>555866916</v>
+        <v>614726242</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>2</v>
@@ -751,7 +756,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>563260847</v>
+        <v>611939491</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>2</v>
@@ -759,7 +764,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>562841365</v>
+        <v>590292920</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>2</v>
@@ -767,7 +772,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>562762959</v>
+        <v>581974023</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>2</v>
@@ -775,7 +780,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>556040164</v>
+        <v>575551704</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>2</v>
@@ -783,7 +788,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>604327696</v>
+        <v>573561374</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>2</v>
@@ -791,7 +796,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>609873314</v>
+        <v>572750903</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>2</v>
@@ -799,7 +804,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>606487530</v>
+        <v>571098635</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>2</v>
@@ -807,79 +812,79 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>597210552</v>
+        <v>608474890</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>596395081</v>
+        <v>751585518</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>595436696</v>
+        <v>757244565</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>595267943</v>
+        <v>756541706</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>590870816</v>
+        <v>756511972</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>590205617</v>
+        <v>756341172</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>569675600</v>
+        <v>755863283</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>713839102</v>
+        <v>755830092</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>693838652</v>
+        <v>696386816</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>175899149</v>
+        <v>737055784</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>4</v>
@@ -887,291 +892,116 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>756098186</v>
+        <v>721254047</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53">
-        <v>760421069</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54">
-        <v>755490848</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B54" s="4"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55">
-        <v>647176340</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56">
-        <v>735443123</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57">
-        <v>757787282</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B57" s="4"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58">
-        <v>757917574</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B58" s="4"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59">
-        <v>701278123</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60">
-        <v>683685592</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61">
-        <v>694378666</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B61" s="4"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62">
-        <v>692339538</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63">
-        <v>690385699</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B63" s="4"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64">
-        <v>678985098</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
-        <v>673687392</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
-        <v>639912074</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
-        <v>647123847</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
-        <v>639625668</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
-        <v>639326366</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
-        <v>634278083</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
-        <v>627014727</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
-        <v>617568591</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73">
-        <v>625201797</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74">
-        <v>623093923</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75">
-        <v>620484463</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76">
-        <v>617466515</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77">
-        <v>617236983</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78">
-        <v>610646246</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79">
-        <v>610347209</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80">
-        <v>605211857</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81">
-        <v>593949500</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82">
-        <v>574682294</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83">
-        <v>566517151</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84">
-        <v>562627814</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85">
-        <v>561574025</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86">
-        <v>555044027</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87">
-        <v>660384995</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="4"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="4"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="4"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="4"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="4"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="4"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="4"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="4"/>
     </row>
     <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
@@ -2762,10 +2592,13 @@
       <c r="B543" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A54">
+  <conditionalFormatting sqref="A53:A54">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:A87">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A55:A87">
+  <conditionalFormatting sqref="A2:A52">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28618"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D46BD1D1-6C98-43CE-8B22-795425092EC2}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7362B0C-E815-43DC-983D-AA10A976227B}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -146,7 +143,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -489,7 +491,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>669100574</v>
+        <v>624587063</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -497,7 +499,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>681109868</v>
+        <v>712838337</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -505,7 +507,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>747820839</v>
+        <v>762484404</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -513,7 +515,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>739687246</v>
+        <v>751487756</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -521,7 +523,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>726843174</v>
+        <v>751156187</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -529,7 +531,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>725868883</v>
+        <v>740264035</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -537,7 +539,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>725868875</v>
+        <v>682824473</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -545,7 +547,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>724644400</v>
+        <v>686470067</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -553,7 +555,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>695292767</v>
+        <v>650690807</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -561,7 +563,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>670930340</v>
+        <v>648138232</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -569,7 +571,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>672168170</v>
+        <v>643772035</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -577,7 +579,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>658886597</v>
+        <v>643198272</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -585,7 +587,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>645870548</v>
+        <v>643066271</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -593,7 +595,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>650250081</v>
+        <v>639781149</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -601,7 +603,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>648791477</v>
+        <v>639583685</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -609,7 +611,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>646421960</v>
+        <v>638207120</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -620,7 +622,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>645278700</v>
+        <v>638198899</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -628,7 +630,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>640633966</v>
+        <v>629527973</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -636,7 +638,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>640393199</v>
+        <v>627656907</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -644,7 +646,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>639504061</v>
+        <v>172497780</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -652,7 +654,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>638567663</v>
+        <v>623502113</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -660,7 +662,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>626969145</v>
+        <v>620168793</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -668,7 +670,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>620524813</v>
+        <v>618365260</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -676,7 +678,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>593551272</v>
+        <v>609697960</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -684,7 +686,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>759646619</v>
+        <v>608157032</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -692,7 +694,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>755265901</v>
+        <v>593604550</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -700,7 +702,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>759572484</v>
+        <v>581395674</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -708,7 +710,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>757556034</v>
+        <v>578274049</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -716,7 +718,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>757138585</v>
+        <v>576126183</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>2</v>
@@ -724,7 +726,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>754586513</v>
+        <v>573718594</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -732,7 +734,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>618972263</v>
+        <v>573391673</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -740,198 +742,103 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>618380608</v>
+        <v>564408874</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34">
-        <v>614726242</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35">
-        <v>611939491</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B35" s="4"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36">
-        <v>590292920</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B36" s="4"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37">
-        <v>581974023</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B37" s="4"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38">
-        <v>575551704</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B38" s="4"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39">
-        <v>573561374</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B39" s="4"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40">
-        <v>572750903</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B40" s="4"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41">
-        <v>571098635</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B41" s="4"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42">
-        <v>608474890</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B42" s="4"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43">
-        <v>751585518</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B43" s="4"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44">
-        <v>757244565</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B44" s="4"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45">
-        <v>756541706</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B45" s="4"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46">
-        <v>756511972</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47">
-        <v>756341172</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B47" s="4"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48">
-        <v>755863283</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>755830092</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>696386816</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>737055784</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>721254047</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="2:2">
       <c r="B53" s="4"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="2:2">
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="2:2">
       <c r="B55" s="4"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="2:2">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="2:2">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="2:2">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="2:2">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="2:2">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="2:2">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="2:2">
       <c r="B62" s="4"/>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="2:2">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="2:2">
       <c r="B64" s="4"/>
     </row>
     <row r="65" spans="2:2">
@@ -2593,12 +2500,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A53:A54">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:A87">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A55:A87">
+  <conditionalFormatting sqref="A34:A52">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A52">
+  <conditionalFormatting sqref="A2:A33">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7362B0C-E815-43DC-983D-AA10A976227B}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C27012F-53EB-44ED-AB6B-8B553C43D29D}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>624587063</v>
+        <v>727904462</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -499,7 +502,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>712838337</v>
+        <v>705842361</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -507,7 +510,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>762484404</v>
+        <v>697066854</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -515,7 +518,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>751487756</v>
+        <v>693768503</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -523,7 +526,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>751156187</v>
+        <v>690494160</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -531,7 +534,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>740264035</v>
+        <v>554683619</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -539,7 +542,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>682824473</v>
+        <v>653491153</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -547,7 +550,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>686470067</v>
+        <v>651698676</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -555,7 +558,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>650690807</v>
+        <v>649320151</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -563,7 +566,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>648138232</v>
+        <v>644369187</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -571,7 +574,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>643772035</v>
+        <v>642690683</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -579,7 +582,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>643198272</v>
+        <v>642556934</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -587,7 +590,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>643066271</v>
+        <v>641887132</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -595,7 +598,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>639781149</v>
+        <v>631803131</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -603,7 +606,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>639583685</v>
+        <v>626601870</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -611,7 +614,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>638207120</v>
+        <v>624969550</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -622,7 +625,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>638198899</v>
+        <v>623800335</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -630,7 +633,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>629527973</v>
+        <v>620660336</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -638,7 +641,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>627656907</v>
+        <v>595817341</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -646,7 +649,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>172497780</v>
+        <v>618427110</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -654,7 +657,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>623502113</v>
+        <v>617682368</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -662,7 +665,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>620168793</v>
+        <v>576603165</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -670,7 +673,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>618365260</v>
+        <v>763007386</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -678,7 +681,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>609697960</v>
+        <v>522323421</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -686,7 +689,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>608157032</v>
+        <v>747823080</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -694,7 +697,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>593604550</v>
+        <v>747822918</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -702,7 +705,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>581395674</v>
+        <v>747814824</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -710,7 +713,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>578274049</v>
+        <v>731403980</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -718,41 +721,51 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>576126183</v>
+        <v>708232503</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>573718594</v>
+        <v>714207697</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>573391673</v>
+        <v>702733001</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>564408874</v>
+        <v>660086723</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="B34" s="4"/>
+      <c r="A34">
+        <v>661303606</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="B35" s="4"/>
+      <c r="A35">
+        <v>762001927</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="4"/>
@@ -2500,15 +2513,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A53:A54">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:A87">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34:A52">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A36:A52">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A33">
+  <conditionalFormatting sqref="A2:A35">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F716F68B-0E29-41E4-8209-36F24B4E7C23}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AECA31A-0D0E-4474-A372-29FDB9CBF9C7}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -484,7 +484,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>685177101</v>
+        <v>697269615</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -492,7 +492,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>634541357</v>
+        <v>773574334</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -500,7 +500,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>627319555</v>
+        <v>775810157</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>630644833</v>
+        <v>775968591</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>614388084</v>
+        <v>773716430</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>587712054</v>
+        <v>754717092</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -532,7 +532,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>608038075</v>
+        <v>767439767</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -540,7 +540,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>603490636</v>
+        <v>768033510</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>602675062</v>
+        <v>767415981</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>598501918</v>
+        <v>767396629</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>698511452</v>
+        <v>767396066</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>711463756</v>
+        <v>767394863</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -580,7 +580,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>713806168</v>
+        <v>767378072</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -588,7 +588,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>700233038</v>
+        <v>767194917</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -596,7 +596,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>702092051</v>
+        <v>767194545</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>695543318</v>
+        <v>766878130</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>695519037</v>
+        <v>749115386</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>682906841</v>
+        <v>752870554</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>656169012</v>
+        <v>743051413</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>644684726</v>
+        <v>742897402</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>647794266</v>
+        <v>740931047</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -655,7 +655,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>643404985</v>
+        <v>583750439</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>639626021</v>
+        <v>602442315</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>634854438</v>
+        <v>604664908</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>653432678</v>
+        <v>603151840</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -687,7 +687,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>653009336</v>
+        <v>602437117</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -695,7 +695,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>652991427</v>
+        <v>591580968</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>652130232</v>
+        <v>589832512</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>649830274</v>
+        <v>585513918</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>2</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>649789512</v>
+        <v>584603181</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -727,7 +727,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>649358136</v>
+        <v>581004219</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>649275439</v>
+        <v>579704812</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>761170319</v>
+        <v>566841049</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>2</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>578476842</v>
+        <v>564098196</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>2</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>554725410</v>
+        <v>712554306</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>570262380</v>
+        <v>727596003</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>2</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>725098309</v>
+        <v>740608249</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>2</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>736846175</v>
+        <v>731390419</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>2</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>737906325</v>
+        <v>736588223</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>2</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>729611909</v>
+        <v>722324591</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>2</v>
@@ -807,7 +807,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>732587260</v>
+        <v>714123019</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>769824354</v>
+        <v>699255505</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>2</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>777201652</v>
+        <v>706501990</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>2</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>769297866</v>
+        <v>698799362</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>2</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>761167786</v>
+        <v>693768677</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>2</v>
@@ -847,87 +847,87 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>765979814</v>
+        <v>670148604</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>727597779</v>
+        <v>685936688</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>736596952</v>
+        <v>676172921</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>767456035</v>
+        <v>684552973</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>567590975</v>
+        <v>682440676</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>175899636</v>
+        <v>670391121</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>767213725</v>
+        <v>664535238</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>764357970</v>
+        <v>646630495</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>764082339</v>
+        <v>647475163</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>764164970</v>
+        <v>654278500</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>575900687</v>
+        <v>651020566</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>2</v>
@@ -935,7 +935,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>750958344</v>
+        <v>646068670</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>2</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>763166349</v>
+        <v>614682981</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>2</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>710562996</v>
+        <v>630843260</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>2</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>723971333</v>
+        <v>639624836</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>2</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>738101835</v>
+        <v>641699123</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>2</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>665649004</v>
+        <v>628270633</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>2</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>691710077</v>
+        <v>626176360</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>2</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>673092627</v>
+        <v>623061433</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>2</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>579756309</v>
+        <v>661059117</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>2</v>
@@ -1007,95 +1007,95 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>646209795</v>
+        <v>660542303</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>649143918</v>
+        <v>693327599</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>648324014</v>
+        <v>175897739</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>646228662</v>
+        <v>780786632</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>628460549</v>
+        <v>741312908</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>626267367</v>
+        <v>766953198</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>625179951</v>
+        <v>767441458</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>615834276</v>
+        <v>767327038</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>524111683</v>
+        <v>766617645</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>169836750</v>
+        <v>766401883</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>173233481</v>
+        <v>175897721</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>173387998</v>
+        <v>714869280</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>4</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>733412104</v>
+        <v>708938802</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>4</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>753257942</v>
+        <v>701913257</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>4</v>
@@ -1119,395 +1119,155 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>764985614</v>
+        <v>705245862</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82">
-        <v>709308930</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B82" s="4"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83">
-        <v>625827096</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84">
-        <v>678569439</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85">
-        <v>685933131</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B85" s="4"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86">
-        <v>693864617</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B86" s="4"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87">
-        <v>653736821</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B87" s="4"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88">
-        <v>644822730</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B88" s="4"/>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89">
-        <v>665201798</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B89" s="4"/>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90">
-        <v>710600358</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B90" s="4"/>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91">
-        <v>765215680</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B91" s="4"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92">
-        <v>749326850</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B92" s="4"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93">
-        <v>736881776</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B93" s="4"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94">
-        <v>702973284</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95">
-        <v>691086007</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B95" s="4"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96">
-        <v>694396015</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97">
-        <v>691490969</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98">
-        <v>667944338</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99">
-        <v>677322699</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100">
-        <v>682086420</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
-        <v>678803192</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102">
-        <v>652423660</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103">
-        <v>589409634</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104">
-        <v>641705227</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105">
-        <v>641069533</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106">
-        <v>640624585</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107">
-        <v>637648746</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108">
-        <v>636255659</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109">
-        <v>633313196</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
-        <v>626744118</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
-        <v>618278372</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112">
-        <v>605487424</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113">
-        <v>599392614</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114">
-        <v>595508114</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115">
-        <v>582856559</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116">
-        <v>580762593</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117">
-        <v>580711723</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118">
-        <v>580281354</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119">
-        <v>579741616</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120">
-        <v>579635065</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121">
-        <v>578515326</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122">
-        <v>576754596</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123">
-        <v>576651818</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124">
-        <v>567783448</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125">
-        <v>563283583</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126">
-        <v>556286502</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127">
-        <v>170324465</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128">
-        <v>760070486</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129">
-        <v>630603789</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B96" s="4"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="4"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="4"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="4"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="4"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="4"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="4"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="4"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="4"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="4"/>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="4"/>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="4"/>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="4"/>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="4"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="4"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="4"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="4"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="4"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="4"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="4"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="4"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="4"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="4"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="4"/>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="4"/>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" s="4"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="4"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="4"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="4"/>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" s="4"/>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="4"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="4"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="4"/>
     </row>
     <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
@@ -3098,10 +2858,10 @@
       <c r="B543" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A56">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A82:A129">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A57:A129">
+  <conditionalFormatting sqref="A2:A81">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AECA31A-0D0E-4474-A372-29FDB9CBF9C7}"/>
+  <xr:revisionPtr revIDLastSave="360" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1A181F5-F374-475D-8805-FE3240E36138}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -484,129 +484,129 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>697269615</v>
-      </c>
-      <c r="B2" s="4" t="s">
+        <v>767979770</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>773574334</v>
-      </c>
-      <c r="B3" s="4" t="s">
+        <v>774212058</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>775810157</v>
-      </c>
-      <c r="B4" s="4" t="s">
+        <v>773840529</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>775968591</v>
-      </c>
-      <c r="B5" s="4" t="s">
+        <v>767979689</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>773716430</v>
-      </c>
-      <c r="B6" s="4" t="s">
+        <v>767979408</v>
+      </c>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>754717092</v>
-      </c>
-      <c r="B7" s="4" t="s">
+        <v>767414596</v>
+      </c>
+      <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>767439767</v>
-      </c>
-      <c r="B8" s="4" t="s">
+        <v>767394376</v>
+      </c>
+      <c r="B8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>768033510</v>
-      </c>
-      <c r="B9" s="4" t="s">
+        <v>767381712</v>
+      </c>
+      <c r="B9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>767415981</v>
-      </c>
-      <c r="B10" s="4" t="s">
+        <v>767326121</v>
+      </c>
+      <c r="B10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>767396629</v>
-      </c>
-      <c r="B11" s="4" t="s">
+        <v>751368006</v>
+      </c>
+      <c r="B11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>767396066</v>
-      </c>
-      <c r="B12" s="4" t="s">
+        <v>763650649</v>
+      </c>
+      <c r="B12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>767394863</v>
-      </c>
-      <c r="B13" s="4" t="s">
+        <v>741351815</v>
+      </c>
+      <c r="B13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>767378072</v>
-      </c>
-      <c r="B14" s="4" t="s">
+        <v>744554266</v>
+      </c>
+      <c r="B14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>767194917</v>
-      </c>
-      <c r="B15" s="4" t="s">
+        <v>689417495</v>
+      </c>
+      <c r="B15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>767194545</v>
-      </c>
-      <c r="B16" s="4" t="s">
+        <v>722663642</v>
+      </c>
+      <c r="B16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>766878130</v>
-      </c>
-      <c r="B17" s="4" t="s">
+        <v>726467057</v>
+      </c>
+      <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="H17" t="s">
@@ -615,351 +615,351 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>749115386</v>
-      </c>
-      <c r="B18" s="4" t="s">
+        <v>727704011</v>
+      </c>
+      <c r="B18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>752870554</v>
-      </c>
-      <c r="B19" s="4" t="s">
+        <v>728467337</v>
+      </c>
+      <c r="B19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>743051413</v>
-      </c>
-      <c r="B20" s="4" t="s">
+        <v>724575844</v>
+      </c>
+      <c r="B20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>742897402</v>
-      </c>
-      <c r="B21" s="4" t="s">
+        <v>700567278</v>
+      </c>
+      <c r="B21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>740931047</v>
-      </c>
-      <c r="B22" s="4" t="s">
+        <v>705999740</v>
+      </c>
+      <c r="B22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>583750439</v>
-      </c>
-      <c r="B23" s="4" t="s">
+        <v>697686396</v>
+      </c>
+      <c r="B23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>602442315</v>
-      </c>
-      <c r="B24" s="4" t="s">
+        <v>653551717</v>
+      </c>
+      <c r="B24" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>604664908</v>
-      </c>
-      <c r="B25" s="4" t="s">
+        <v>666334044</v>
+      </c>
+      <c r="B25" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>603151840</v>
-      </c>
-      <c r="B26" s="4" t="s">
+        <v>678594924</v>
+      </c>
+      <c r="B26" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>602437117</v>
-      </c>
-      <c r="B27" s="4" t="s">
+        <v>684404209</v>
+      </c>
+      <c r="B27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>591580968</v>
-      </c>
-      <c r="B28" s="4" t="s">
+        <v>685460267</v>
+      </c>
+      <c r="B28" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>589832512</v>
-      </c>
-      <c r="B29" s="4" t="s">
+        <v>674685890</v>
+      </c>
+      <c r="B29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>585513918</v>
-      </c>
-      <c r="B30" s="4" t="s">
+        <v>665637751</v>
+      </c>
+      <c r="B30" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>584603181</v>
-      </c>
-      <c r="B31" s="4" t="s">
+        <v>655393035</v>
+      </c>
+      <c r="B31" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>581004219</v>
-      </c>
-      <c r="B32" s="4" t="s">
+        <v>658035534</v>
+      </c>
+      <c r="B32" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>579704812</v>
-      </c>
-      <c r="B33" s="4" t="s">
+        <v>653780571</v>
+      </c>
+      <c r="B33" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>566841049</v>
-      </c>
-      <c r="B34" s="4" t="s">
+        <v>638057178</v>
+      </c>
+      <c r="B34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>564098196</v>
-      </c>
-      <c r="B35" s="4" t="s">
+        <v>637735717</v>
+      </c>
+      <c r="B35" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>712554306</v>
-      </c>
-      <c r="B36" s="4" t="s">
+        <v>630827818</v>
+      </c>
+      <c r="B36" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>727596003</v>
-      </c>
-      <c r="B37" s="4" t="s">
+        <v>630778615</v>
+      </c>
+      <c r="B37" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>740608249</v>
-      </c>
-      <c r="B38" s="4" t="s">
+        <v>622033557</v>
+      </c>
+      <c r="B38" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>731390419</v>
-      </c>
-      <c r="B39" s="4" t="s">
+        <v>629469291</v>
+      </c>
+      <c r="B39" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>736588223</v>
-      </c>
-      <c r="B40" s="4" t="s">
+        <v>630242976</v>
+      </c>
+      <c r="B40" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>722324591</v>
-      </c>
-      <c r="B41" s="4" t="s">
+        <v>623963026</v>
+      </c>
+      <c r="B41" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>714123019</v>
-      </c>
-      <c r="B42" s="4" t="s">
+        <v>576063923</v>
+      </c>
+      <c r="B42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>699255505</v>
-      </c>
-      <c r="B43" s="4" t="s">
+        <v>595179817</v>
+      </c>
+      <c r="B43" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>706501990</v>
-      </c>
-      <c r="B44" s="4" t="s">
+        <v>605331564</v>
+      </c>
+      <c r="B44" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>698799362</v>
-      </c>
-      <c r="B45" s="4" t="s">
+        <v>613189707</v>
+      </c>
+      <c r="B45" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>693768677</v>
-      </c>
-      <c r="B46" s="4" t="s">
+        <v>603038526</v>
+      </c>
+      <c r="B46" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>670148604</v>
-      </c>
-      <c r="B47" s="4" t="s">
+        <v>593925575</v>
+      </c>
+      <c r="B47" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>685936688</v>
-      </c>
-      <c r="B48" s="4" t="s">
+        <v>583828474</v>
+      </c>
+      <c r="B48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>676172921</v>
-      </c>
-      <c r="B49" s="4" t="s">
+        <v>583756246</v>
+      </c>
+      <c r="B49" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>684552973</v>
-      </c>
-      <c r="B50" s="4" t="s">
+        <v>581616848</v>
+      </c>
+      <c r="B50" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>682440676</v>
-      </c>
-      <c r="B51" s="4" t="s">
+        <v>581599218</v>
+      </c>
+      <c r="B51" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>670391121</v>
-      </c>
-      <c r="B52" s="4" t="s">
+        <v>581399668</v>
+      </c>
+      <c r="B52" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>664535238</v>
-      </c>
-      <c r="B53" s="4" t="s">
+        <v>173648498</v>
+      </c>
+      <c r="B53" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>646630495</v>
-      </c>
-      <c r="B54" s="4" t="s">
+        <v>561160486</v>
+      </c>
+      <c r="B54" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>647475163</v>
-      </c>
-      <c r="B55" s="4" t="s">
+        <v>570923957</v>
+      </c>
+      <c r="B55" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>654278500</v>
-      </c>
-      <c r="B56" s="4" t="s">
+        <v>554651962</v>
+      </c>
+      <c r="B56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>651020566</v>
-      </c>
-      <c r="B57" s="4" t="s">
+        <v>172459079</v>
+      </c>
+      <c r="B57" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>646068670</v>
-      </c>
-      <c r="B58" s="4" t="s">
+        <v>170345627</v>
+      </c>
+      <c r="B58" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>614682981</v>
-      </c>
-      <c r="B59" s="4" t="s">
+        <v>170153435</v>
+      </c>
+      <c r="B59" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>630843260</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>2</v>
+        <v>675365062</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>639624836</v>
+        <v>773574334</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>2</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>641699123</v>
+        <v>775810157</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>2</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>628270633</v>
+        <v>775968591</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>2</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>626176360</v>
+        <v>773716430</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>2</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>623061433</v>
+        <v>754717092</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>2</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>661059117</v>
+        <v>767439767</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>2</v>
@@ -1007,267 +1007,587 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>660542303</v>
+        <v>768033510</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>693327599</v>
+        <v>767415981</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>175897739</v>
+        <v>767396629</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>780786632</v>
+        <v>767396066</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>741312908</v>
+        <v>767394863</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>766953198</v>
+        <v>767378072</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>767441458</v>
+        <v>767194917</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>767327038</v>
+        <v>767194545</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>766617645</v>
+        <v>766878130</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>766401883</v>
+        <v>749115386</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>175897721</v>
+        <v>752870554</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>714869280</v>
+        <v>743051413</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>708938802</v>
+        <v>742897402</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>701913257</v>
+        <v>740931047</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
+        <v>583750439</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>602442315</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>604664908</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>603151840</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>602437117</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>591580968</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>589832512</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>585513918</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>584603181</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>581004219</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>579704812</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>566841049</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>564098196</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>712554306</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>727596003</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>740608249</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>731390419</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>736588223</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>722324591</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>714123019</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>699255505</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>706501990</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>698799362</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>693768677</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>670148604</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>685936688</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>676172921</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>684552973</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>682440676</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>670391121</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>664535238</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>646630495</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>647475163</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>654278500</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>651020566</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>646068670</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>614682981</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>630843260</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>639624836</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>641699123</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>628270633</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>626176360</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>623061433</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>661059117</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>660542303</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>693327599</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>175897739</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>780786632</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>741312908</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>766953198</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>767441458</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>767327038</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>766617645</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>766401883</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>175897721</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>714869280</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>708938802</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>701913257</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
         <v>705245862</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B139" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="B82" s="4"/>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="B83" s="4"/>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="B84" s="4"/>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="B85" s="4"/>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="B86" s="4"/>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="B87" s="4"/>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="B88" s="4"/>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="B89" s="4"/>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="B90" s="4"/>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="B91" s="4"/>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="B92" s="4"/>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" s="4"/>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="B94" s="4"/>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="B95" s="4"/>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="B96" s="4"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="4"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="4"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="4"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="4"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="4"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="4"/>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" s="4"/>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="4"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="4"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="4"/>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="4"/>
-    </row>
-    <row r="108" spans="2:2">
-      <c r="B108" s="4"/>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" s="4"/>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" s="4"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="4"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="4"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="4"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="4"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="4"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="4"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="4"/>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" s="4"/>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="4"/>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="4"/>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121" s="4"/>
-    </row>
-    <row r="122" spans="2:2">
-      <c r="B122" s="4"/>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="4"/>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="4"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="4"/>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="4"/>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="4"/>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128" s="4"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="4"/>
     </row>
     <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
@@ -2858,10 +3178,10 @@
       <c r="B543" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A82:A129">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  <conditionalFormatting sqref="A2:A60">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A81">
+  <conditionalFormatting sqref="A61:A139">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD56B63-3885-4453-9094-0B7D3ED41B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFE8DAFB-8610-4CF1-BE2F-5720F4C94E6A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
+    <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -57,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -476,13 +476,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
   <dimension ref="A1:H543"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="65.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,129 +490,129 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>779257827</v>
+        <v>722619271</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3">
-        <v>640463307</v>
+        <v>734719028</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4">
-        <v>664361536</v>
+        <v>743204210</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5">
-        <v>662663792</v>
+        <v>602626909</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6">
-        <v>658143643</v>
+        <v>582785717</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>657922641</v>
+        <v>591403799</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8">
-        <v>657783597</v>
+        <v>586335782</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
-        <v>657656231</v>
+        <v>567210897</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
-        <v>653502926</v>
+        <v>628642203</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
-        <v>648378267</v>
+        <v>627011756</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>620103279</v>
+        <v>626159671</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13">
-        <v>632170498</v>
+        <v>622874281</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>622487399</v>
+        <v>621494362</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15">
-        <v>573936196</v>
+        <v>607057571</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16">
-        <v>616110122</v>
+        <v>597921513</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17">
-        <v>773723170</v>
+        <v>748984287</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>2</v>
@@ -621,2023 +621,2403 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18">
-        <v>773516905</v>
+        <v>776553608</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19">
-        <v>770800427</v>
+        <v>172580700</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20">
-        <v>772721100</v>
+        <v>544321361</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21">
-        <v>749786855</v>
+        <v>175205917</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22">
-        <v>754114969</v>
+        <v>175205909</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23">
-        <v>757389196</v>
+        <v>774225787</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8">
       <c r="A24">
-        <v>748446428</v>
+        <v>774136729</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25">
-        <v>748445958</v>
+        <v>774101335</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26">
-        <v>744174222</v>
+        <v>770152472</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27">
-        <v>731872200</v>
+        <v>766891984</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28">
-        <v>716857929</v>
+        <v>767042496</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29">
-        <v>667941375</v>
+        <v>726520079</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30">
-        <v>685946232</v>
+        <v>727474730</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31">
-        <v>677237343</v>
+        <v>698942491</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32">
-        <v>672925710</v>
+        <v>663649063</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33">
-        <v>722085481</v>
+        <v>633284397</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34">
-        <v>700781259</v>
+        <v>633152164</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35">
-        <v>716611334</v>
+        <v>667056810</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>651417952</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>655285033</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>652841754</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>652388681</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>652355599</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>652225487</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>652221346</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>640875609</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>644139598</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>639722465</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>702417571</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>714178567</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>716223577</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>706801580</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>704862998</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>648471872</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>772608950</v>
-      </c>
-      <c r="B36" s="5" t="s">
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>730855800</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>647401086</v>
-      </c>
-      <c r="B37" s="5" t="s">
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>772814376</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>175876550</v>
-      </c>
-      <c r="B38" s="5" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>772497768</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>729247480</v>
-      </c>
-      <c r="B39" s="5" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>762762189</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>788756256</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="4"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="4"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="4"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="4"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="4"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="4"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67" s="4"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68" s="4"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69" s="4"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="4"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="4"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="4"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="4"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="4"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="4"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76" s="4"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="4"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="4"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79" s="4"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="4"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="4"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="4"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="4"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="4"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="4"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="4"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="4"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="4"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="4"/>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="4"/>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="4"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="4"/>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="4"/>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="4"/>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="4"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="4"/>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97" s="4"/>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="4"/>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="4"/>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100" s="4"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="4"/>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="4"/>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103" s="4"/>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="4"/>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>742869641</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>749593400</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>745164651</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>778211916</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>720499072</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>746434715</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>754729501</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>774717809</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>773930239</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>767361110</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>754407637</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>754114977</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>744363361</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>742364726</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>738114465</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>705220592</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>713868341</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>717107563</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>514274723</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>636138152</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>671502486</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>670180912</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>668898749</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>666163039</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>661254361</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>655712564</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>654732514</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>654384134</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>648233421</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>645037619</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>612909865</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>632456327</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>629774492</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>628150843</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>591906544</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>587266622</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>583228790</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>172586301</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>779914138</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>779396096</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>657713081</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>700935640</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>767157401</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>772612804</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>772246967</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>699468926</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>682148980</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>683613784</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>661217319</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="B105" s="4"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2">
       <c r="B106" s="4"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2">
       <c r="B107" s="4"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2">
       <c r="B108" s="4"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2">
       <c r="B109" s="4"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2">
       <c r="B110" s="4"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2">
       <c r="B111" s="4"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2">
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:2">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:2">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:2">
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:2">
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:2">
       <c r="B117" s="4"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:2">
       <c r="B118" s="4"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:2">
       <c r="B119" s="4"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:2">
       <c r="B120" s="4"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:2">
       <c r="B121" s="4"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:2">
       <c r="B122" s="4"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:2">
       <c r="B123" s="4"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:2">
       <c r="B124" s="4"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:2">
       <c r="B125" s="4"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:2">
       <c r="B126" s="4"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:2">
       <c r="B127" s="4"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:2">
       <c r="B128" s="4"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:2">
       <c r="B129" s="4"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:2">
       <c r="B130" s="4"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2">
       <c r="B131" s="4"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:2">
       <c r="B132" s="4"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:2">
       <c r="B133" s="4"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:2">
       <c r="B134" s="4"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:2">
       <c r="B135" s="4"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:2">
       <c r="B136" s="4"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:2">
       <c r="B137" s="4"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:2">
       <c r="B138" s="4"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:2">
       <c r="B139" s="4"/>
     </row>
-    <row r="147" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
     </row>
-    <row r="148" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="15">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
     </row>
-    <row r="149" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="15">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
     </row>
-    <row r="150" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="15">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
     </row>
-    <row r="151" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="15">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
     </row>
-    <row r="152" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="15">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
     </row>
-    <row r="153" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="15">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
     </row>
-    <row r="154" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="15">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
     </row>
-    <row r="155" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="15">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
     </row>
-    <row r="156" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="15">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
     </row>
-    <row r="157" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="15">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
     </row>
-    <row r="158" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="15">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
     </row>
-    <row r="159" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="15">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
     </row>
-    <row r="160" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="15">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
     </row>
-    <row r="161" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="15">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
     </row>
-    <row r="162" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="15">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
     </row>
-    <row r="163" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="15">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
     </row>
-    <row r="164" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="15">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
     </row>
-    <row r="165" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="15">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
     </row>
-    <row r="166" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="15">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
     </row>
-    <row r="167" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="15">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
     </row>
-    <row r="168" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="15">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
     </row>
-    <row r="169" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="15">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
     </row>
-    <row r="170" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="15">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
     </row>
-    <row r="171" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="15">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
     </row>
-    <row r="172" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="15">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
     </row>
-    <row r="173" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="15">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
     </row>
-    <row r="174" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="15">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
     </row>
-    <row r="175" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="15">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
     </row>
-    <row r="176" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="15">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
     </row>
-    <row r="177" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="15">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
     </row>
-    <row r="178" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="15">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
     </row>
-    <row r="179" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="15">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
     </row>
-    <row r="180" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="15">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
     </row>
-    <row r="181" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="15">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
     </row>
-    <row r="182" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="15">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
     </row>
-    <row r="183" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="15">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
     </row>
-    <row r="184" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="15">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
     </row>
-    <row r="185" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="15">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
     </row>
-    <row r="186" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="15">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
     </row>
-    <row r="187" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="15">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
     </row>
-    <row r="188" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="15">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
     </row>
-    <row r="189" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="15">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
     </row>
-    <row r="190" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="15">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
     </row>
-    <row r="191" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="15">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
     </row>
-    <row r="192" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="15">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
     </row>
-    <row r="193" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="15">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
     </row>
-    <row r="194" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="15">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
     </row>
-    <row r="195" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="15">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
     </row>
-    <row r="196" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="15">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
     </row>
-    <row r="197" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="15">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
     </row>
-    <row r="198" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="15">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
     </row>
-    <row r="199" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="15">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
     </row>
-    <row r="200" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="15">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
     </row>
-    <row r="201" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="15">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
     </row>
-    <row r="202" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="15">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
     </row>
-    <row r="203" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="15">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
     </row>
-    <row r="204" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="15">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
     </row>
-    <row r="205" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="15">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
     </row>
-    <row r="206" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="15">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
     </row>
-    <row r="207" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="15">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
     </row>
-    <row r="208" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="15">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
     </row>
-    <row r="209" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" ht="15">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
     </row>
-    <row r="210" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="15">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
     </row>
-    <row r="211" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" ht="15">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
     </row>
-    <row r="212" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" ht="15">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
     </row>
-    <row r="213" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" ht="15">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
     </row>
-    <row r="214" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" ht="15">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
     </row>
-    <row r="215" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" ht="15">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
     </row>
-    <row r="216" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" ht="15">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
     </row>
-    <row r="217" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" ht="15">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
     </row>
-    <row r="218" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" ht="15">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
     </row>
-    <row r="219" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" ht="15">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
     </row>
-    <row r="220" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" ht="15">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
     </row>
-    <row r="221" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" ht="15">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
     </row>
-    <row r="222" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" ht="15">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
     </row>
-    <row r="223" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" ht="15">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
     </row>
-    <row r="224" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" ht="15">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
     </row>
-    <row r="225" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="15">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
     </row>
-    <row r="226" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="15">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
     </row>
-    <row r="227" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="15">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
     </row>
-    <row r="228" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="15">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
     </row>
-    <row r="229" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="15">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
     </row>
-    <row r="230" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="15">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
     </row>
-    <row r="231" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="15">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
     </row>
-    <row r="232" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="15">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
     </row>
-    <row r="233" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="15">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
     </row>
-    <row r="234" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="15">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
     </row>
-    <row r="235" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="15">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
     </row>
-    <row r="236" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="15">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
     </row>
-    <row r="237" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="15">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
     </row>
-    <row r="238" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="15">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
     </row>
-    <row r="239" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="15">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
     </row>
-    <row r="240" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="15">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
     </row>
-    <row r="241" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="15">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
     </row>
-    <row r="242" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="15">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
     </row>
-    <row r="243" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="15">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
     </row>
-    <row r="244" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="15">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
     </row>
-    <row r="245" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="15">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
     </row>
-    <row r="246" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="15">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
     </row>
-    <row r="247" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="15">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
     </row>
-    <row r="248" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="15">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
     </row>
-    <row r="249" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="15">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
     </row>
-    <row r="250" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="15">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
     </row>
-    <row r="251" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="15">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
     </row>
-    <row r="252" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="15">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
     </row>
-    <row r="253" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="15">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
     </row>
-    <row r="254" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="15">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
     </row>
-    <row r="255" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="15">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
     </row>
-    <row r="256" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="15">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
     </row>
-    <row r="257" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="15">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
     </row>
-    <row r="258" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="15">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
     </row>
-    <row r="259" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="15">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
     </row>
-    <row r="260" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="15">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
     </row>
-    <row r="261" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="15">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
     </row>
-    <row r="262" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="15">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
     </row>
-    <row r="263" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="15">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
     </row>
-    <row r="264" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="15">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
     </row>
-    <row r="265" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="15">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
     </row>
-    <row r="266" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="15">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
     </row>
-    <row r="267" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="15">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
     </row>
-    <row r="268" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="15">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
     </row>
-    <row r="269" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="15">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
     </row>
-    <row r="270" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="15">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
     </row>
-    <row r="271" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="15">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
     </row>
-    <row r="272" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="15">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
     </row>
-    <row r="273" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="15">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
     </row>
-    <row r="274" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="15">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
     </row>
-    <row r="275" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="15">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
     </row>
-    <row r="276" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="15">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
     </row>
-    <row r="277" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="15">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
     </row>
-    <row r="278" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="15">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
     </row>
-    <row r="279" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="15">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
     </row>
-    <row r="280" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="15">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
     </row>
-    <row r="281" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="15">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
     </row>
-    <row r="282" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="15">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
     </row>
-    <row r="283" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="15">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
     </row>
-    <row r="284" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="15">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
     </row>
-    <row r="285" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="15">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
     </row>
-    <row r="286" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="15">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
     </row>
-    <row r="287" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="15">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
     </row>
-    <row r="288" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="15">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
     </row>
-    <row r="289" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="15">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
     </row>
-    <row r="290" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="15">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
     </row>
-    <row r="291" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="15">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
     </row>
-    <row r="292" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="15">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
     </row>
-    <row r="293" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="15">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
     </row>
-    <row r="294" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="15">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
     </row>
-    <row r="295" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="15">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
     </row>
-    <row r="296" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="15">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
     </row>
-    <row r="297" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="15">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
     </row>
-    <row r="298" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="15">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
     </row>
-    <row r="299" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="15">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
     </row>
-    <row r="300" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="15">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
     </row>
-    <row r="301" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="15">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
     </row>
-    <row r="302" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="15">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
     </row>
-    <row r="303" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="15">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
     </row>
-    <row r="304" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="15">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
     </row>
-    <row r="305" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="15">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
     </row>
-    <row r="306" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="15">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
     </row>
-    <row r="307" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="15">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
     </row>
-    <row r="308" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="15">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
     </row>
-    <row r="309" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="15">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
     </row>
-    <row r="310" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="15">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
     </row>
-    <row r="311" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="15">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
     </row>
-    <row r="312" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="15">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
     </row>
-    <row r="313" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" ht="15">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
     </row>
-    <row r="314" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" ht="15">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
     </row>
-    <row r="315" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" ht="15">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
     </row>
-    <row r="316" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" ht="15">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
     </row>
-    <row r="317" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" ht="15">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
     </row>
-    <row r="318" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" ht="15">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
     </row>
-    <row r="319" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" ht="15">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
     </row>
-    <row r="320" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" ht="15">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
     </row>
-    <row r="321" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="15">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
     </row>
-    <row r="322" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="15">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
     </row>
-    <row r="323" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="15">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
     </row>
-    <row r="324" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="15">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
     </row>
-    <row r="325" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="15">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
     </row>
-    <row r="326" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="15">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
     </row>
-    <row r="327" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="15">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
     </row>
-    <row r="328" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="15">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
     </row>
-    <row r="329" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="15">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
     </row>
-    <row r="330" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="15">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
     </row>
-    <row r="331" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="15">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
     </row>
-    <row r="332" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="15">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
     </row>
-    <row r="333" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="15">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
     </row>
-    <row r="334" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="15">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
     </row>
-    <row r="335" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="15">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
     </row>
-    <row r="336" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="15">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
     </row>
-    <row r="337" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="15">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
     </row>
-    <row r="338" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="15">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
     </row>
-    <row r="339" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="15">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
     </row>
-    <row r="340" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="15">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
     </row>
-    <row r="341" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="15">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
     </row>
-    <row r="342" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="15">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
     </row>
-    <row r="343" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="15">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
     </row>
-    <row r="344" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="15">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
     </row>
-    <row r="345" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="15">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
     </row>
-    <row r="346" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="15">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
     </row>
-    <row r="347" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="15">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
     </row>
-    <row r="348" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="15">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
     </row>
-    <row r="349" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="15">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
     </row>
-    <row r="350" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="15">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
     </row>
-    <row r="351" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="15">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
     </row>
-    <row r="352" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="15">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
     </row>
-    <row r="353" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="15">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
     </row>
-    <row r="354" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="15">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
     </row>
-    <row r="355" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="15">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
     </row>
-    <row r="356" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="15">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
     </row>
-    <row r="357" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="15">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
     </row>
-    <row r="358" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="15">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
     </row>
-    <row r="359" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="15">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
     </row>
-    <row r="360" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="15">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
     </row>
-    <row r="361" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="15">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
     </row>
-    <row r="362" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="15">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
     </row>
-    <row r="363" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="15">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
     </row>
-    <row r="364" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="15">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
     </row>
-    <row r="365" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="15">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
     </row>
-    <row r="366" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="15">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
     </row>
-    <row r="367" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="15">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
     </row>
-    <row r="368" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" ht="15">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
     </row>
-    <row r="369" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="15">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
     </row>
-    <row r="370" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="15">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
     </row>
-    <row r="371" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="15">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
     </row>
-    <row r="372" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="15">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
     </row>
-    <row r="373" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="15">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
     </row>
-    <row r="374" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="15">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
     </row>
-    <row r="375" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="15">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
     </row>
-    <row r="376" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="15">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
     </row>
-    <row r="377" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="15">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
     </row>
-    <row r="378" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="15">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
     </row>
-    <row r="379" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="15">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
     </row>
-    <row r="380" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="15">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
     </row>
-    <row r="381" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="15">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
     </row>
-    <row r="382" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="15">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
     </row>
-    <row r="383" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="15">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
     </row>
-    <row r="384" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="15">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
     </row>
-    <row r="385" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="15">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
     </row>
-    <row r="386" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="15">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
     </row>
-    <row r="387" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="15">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
     </row>
-    <row r="388" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="15">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
     </row>
-    <row r="389" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="15">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
     </row>
-    <row r="390" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="15">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
     </row>
-    <row r="391" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="15">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
     </row>
-    <row r="392" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="15">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
     </row>
-    <row r="393" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="15">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
     </row>
-    <row r="394" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="15">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
     </row>
-    <row r="395" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="15">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
     </row>
-    <row r="396" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="15">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
     </row>
-    <row r="397" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="15">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
     </row>
-    <row r="398" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="15">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
     </row>
-    <row r="399" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="15">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
     </row>
-    <row r="400" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="15">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
     </row>
-    <row r="401" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="15">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
     </row>
-    <row r="402" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="15">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
     </row>
-    <row r="403" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="15">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
     </row>
-    <row r="404" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="15">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
     </row>
-    <row r="405" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="15">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
     </row>
-    <row r="406" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="15">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
     </row>
-    <row r="407" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="15">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
     </row>
-    <row r="408" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="15">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
     </row>
-    <row r="409" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="15">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
     </row>
-    <row r="410" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="15">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
     </row>
-    <row r="411" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="15">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
     </row>
-    <row r="412" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="15">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
     </row>
-    <row r="413" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="15">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
     </row>
-    <row r="414" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="15">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
     </row>
-    <row r="415" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="15">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
     </row>
-    <row r="416" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="15">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
     </row>
-    <row r="417" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" ht="15">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
     </row>
-    <row r="418" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" ht="15">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
     </row>
-    <row r="419" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" ht="15">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
     </row>
-    <row r="420" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" ht="15">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
     </row>
-    <row r="421" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" ht="15">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
     </row>
-    <row r="422" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" ht="15">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
     </row>
-    <row r="423" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" ht="15">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
     </row>
-    <row r="424" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" ht="15">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
     </row>
-    <row r="425" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" ht="15">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
     </row>
-    <row r="426" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" ht="15">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
     </row>
-    <row r="427" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" ht="15">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
     </row>
-    <row r="428" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" ht="15">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
     </row>
-    <row r="429" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" ht="15">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
     </row>
-    <row r="430" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" ht="15">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
     </row>
-    <row r="431" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" ht="15">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
     </row>
-    <row r="432" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" ht="15">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
     </row>
-    <row r="433" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="15">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
     </row>
-    <row r="434" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="15">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
     </row>
-    <row r="435" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="15">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
     </row>
-    <row r="436" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="15">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
     </row>
-    <row r="437" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="15">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
     </row>
-    <row r="438" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="15">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
     </row>
-    <row r="439" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="15">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
     </row>
-    <row r="440" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="15">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
     </row>
-    <row r="441" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="15">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
     </row>
-    <row r="442" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="15">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
     </row>
-    <row r="443" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="15">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
     </row>
-    <row r="444" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="15">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
     </row>
-    <row r="445" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="15">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
     </row>
-    <row r="446" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="15">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
     </row>
-    <row r="447" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="15">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
     </row>
-    <row r="448" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="15">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
     </row>
-    <row r="449" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="15">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
     </row>
-    <row r="450" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="15">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
     </row>
-    <row r="451" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="15">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
     </row>
-    <row r="452" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="15">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
     </row>
-    <row r="453" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="15">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
     </row>
-    <row r="454" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="15">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
     </row>
-    <row r="455" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="15">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
     </row>
-    <row r="456" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="15">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
     </row>
-    <row r="457" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="15">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
     </row>
-    <row r="458" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="15">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
     </row>
-    <row r="459" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="15">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
     </row>
-    <row r="460" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="15">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
     </row>
-    <row r="461" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="15">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
     </row>
-    <row r="462" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="15">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
     </row>
-    <row r="463" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="15">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
     </row>
-    <row r="464" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="15">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
     </row>
-    <row r="465" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="15">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
     </row>
-    <row r="466" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="15">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
     </row>
-    <row r="467" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="15">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
     </row>
-    <row r="468" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="15">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
     </row>
-    <row r="469" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="15">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
     </row>
-    <row r="470" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="15">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
     </row>
-    <row r="471" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="15">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
     </row>
-    <row r="472" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="15">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
     </row>
-    <row r="473" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="15">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
     </row>
-    <row r="474" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="15">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
     </row>
-    <row r="475" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="15">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
     </row>
-    <row r="476" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="15">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
     </row>
-    <row r="477" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="15">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
     </row>
-    <row r="478" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="15">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
     </row>
-    <row r="479" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="15">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
     </row>
-    <row r="480" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="15">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
     </row>
-    <row r="481" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="15">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
     </row>
-    <row r="482" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="15">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
     </row>
-    <row r="483" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="15">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
     </row>
-    <row r="484" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="15">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
     </row>
-    <row r="485" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="15">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
     </row>
-    <row r="486" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="15">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
     </row>
-    <row r="487" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="15">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
     </row>
-    <row r="488" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="15">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
     </row>
-    <row r="489" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="15">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
     </row>
-    <row r="490" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="15">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
     </row>
-    <row r="491" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="15">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
     </row>
-    <row r="492" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="15">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
     </row>
-    <row r="493" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="15">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
     </row>
-    <row r="494" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="15">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
     </row>
-    <row r="495" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="15">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
     </row>
-    <row r="496" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="15">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
     </row>
-    <row r="497" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="15">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
     </row>
-    <row r="498" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="15">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
     </row>
-    <row r="499" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="15">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
     </row>
-    <row r="500" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="15">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
     </row>
-    <row r="501" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" ht="15">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
     </row>
-    <row r="502" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" ht="15">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
     </row>
-    <row r="503" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" ht="15">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
     </row>
-    <row r="504" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" ht="15">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
     </row>
-    <row r="505" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" ht="15">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
     </row>
-    <row r="506" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" ht="15">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
     </row>
-    <row r="507" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" ht="15">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
     </row>
-    <row r="508" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" ht="15">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
     </row>
-    <row r="509" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" ht="15">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
     </row>
-    <row r="510" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" ht="15">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
     </row>
-    <row r="511" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" ht="15">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
     </row>
-    <row r="512" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" ht="15">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
     </row>
-    <row r="513" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" ht="15">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
     </row>
-    <row r="514" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" ht="15">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
     </row>
-    <row r="515" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" ht="15">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
     </row>
-    <row r="516" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" ht="15">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
     </row>
-    <row r="517" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" ht="15">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
     </row>
-    <row r="518" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" ht="15">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
     </row>
-    <row r="519" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" ht="15">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
     </row>
-    <row r="520" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" ht="15">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
     </row>
-    <row r="521" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" ht="15">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
     </row>
-    <row r="522" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" ht="15">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
     </row>
-    <row r="523" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" ht="15">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
     </row>
-    <row r="524" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" ht="15">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
     </row>
-    <row r="525" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" ht="15">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
     </row>
-    <row r="526" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" ht="15">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
     </row>
-    <row r="527" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" ht="15">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
     </row>
-    <row r="528" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" ht="15">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
     </row>
-    <row r="529" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" ht="15">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
     </row>
-    <row r="530" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" ht="15">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
     </row>
-    <row r="531" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" ht="15">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
     </row>
-    <row r="532" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" ht="15">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
     </row>
-    <row r="533" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" ht="15">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
     </row>
-    <row r="534" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" ht="15">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
     </row>
-    <row r="535" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" ht="15">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
     </row>
-    <row r="536" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" ht="15">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
     </row>
-    <row r="537" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" ht="15">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
     </row>
-    <row r="538" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" ht="15">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
     </row>
-    <row r="539" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" ht="15">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
     </row>
-    <row r="540" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" ht="15">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
     </row>
-    <row r="541" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" ht="15">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
     </row>
-    <row r="542" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" ht="15">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
     </row>
-    <row r="543" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" ht="15">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A41:A60">
+  <conditionalFormatting sqref="A105:A139">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61:A139">
+  <conditionalFormatting sqref="A2:A60">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A40">
+  <conditionalFormatting sqref="A61:A104">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar (1).xlsx
+++ b/Treinamento/Planilha Robô Regularizar (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3DF2EA-11C3-488F-BB85-75C0861C6A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C872C44-8BB1-485E-BE90-E70B3E81C60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -143,12 +143,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -464,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B425"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -481,7 +476,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>734719036</v>
+        <v>625852813</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -489,7 +484,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>738478183</v>
+        <v>691303071</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -497,7 +492,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>737391213</v>
+        <v>727904470</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -505,7 +500,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>697567026</v>
+        <v>762886897</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -513,7 +508,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>716879824</v>
+        <v>753878754</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -521,7 +516,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>721408841</v>
+        <v>738114473</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -529,7 +524,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>720493273</v>
+        <v>689591349</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -537,7 +532,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>708313766</v>
+        <v>685864617</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -545,7 +540,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>698942509</v>
+        <v>684555356</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -553,7 +548,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>697714578</v>
+        <v>684154390</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -561,7 +556,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>686734835</v>
+        <v>678430129</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -569,7 +564,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>673923813</v>
+        <v>677344107</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -577,7 +572,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>674710268</v>
+        <v>655859290</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -585,7 +580,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>677322707</v>
+        <v>664576216</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -593,7 +588,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>673691741</v>
+        <v>664380791</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -601,7 +596,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>661466429</v>
+        <v>652140421</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -609,7 +604,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>666759588</v>
+        <v>652423678</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -617,7 +612,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>655709206</v>
+        <v>652225495</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -625,7 +620,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>655586380</v>
+        <v>648122749</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -633,7 +628,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>652836275</v>
+        <v>629835996</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -641,7 +636,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>598501926</v>
+        <v>624987933</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -649,7 +644,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>626858165</v>
+        <v>624941302</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -657,7 +652,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>650243540</v>
+        <v>579584941</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -665,7 +660,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>649105297</v>
+        <v>785342902</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -673,7 +668,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>648610628</v>
+        <v>801330048</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -681,7 +676,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>642608073</v>
+        <v>801278072</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -689,7 +684,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>643498318</v>
+        <v>785343124</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -697,7 +692,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>637483284</v>
+        <v>789399239</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -705,7 +700,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>636264495</v>
+        <v>789399122</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>2</v>
@@ -713,7 +708,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>628731469</v>
+        <v>778737969</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -721,7 +716,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>624690818</v>
+        <v>610122669</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -729,7 +724,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>613784168</v>
+        <v>606279978</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
@@ -737,7 +732,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>604680326</v>
+        <v>599369331</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>2</v>
@@ -745,7 +740,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>172801981</v>
+        <v>564979452</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>2</v>
@@ -753,7 +748,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>574359844</v>
+        <v>175815715</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>2</v>
@@ -761,7 +756,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>780295691</v>
+        <v>175107287</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>2</v>
@@ -769,23 +764,23 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>789391947</v>
+        <v>174761373</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>720022312</v>
+        <v>174196273</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>615098617</v>
+        <v>794929681</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>3</v>
@@ -793,7 +788,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>682478718</v>
+        <v>794575492</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>3</v>
@@ -801,27 +796,43 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>794177752</v>
+        <v>794218382</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>789173832</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>675615045</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>749593418</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>779518509</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
@@ -2083,264 +2094,8 @@
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
     </row>
-    <row r="362" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A362" s="3"/>
-      <c r="B362" s="3"/>
-    </row>
-    <row r="363" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A363" s="3"/>
-      <c r="B363" s="3"/>
-    </row>
-    <row r="364" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A364" s="3"/>
-      <c r="B364" s="3"/>
-    </row>
-    <row r="365" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A365" s="3"/>
-      <c r="B365" s="3"/>
-    </row>
-    <row r="366" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A366" s="3"/>
-      <c r="B366" s="3"/>
-    </row>
-    <row r="367" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A367" s="3"/>
-      <c r="B367" s="3"/>
-    </row>
-    <row r="368" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A368" s="3"/>
-      <c r="B368" s="3"/>
-    </row>
-    <row r="369" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A369" s="3"/>
-      <c r="B369" s="3"/>
-    </row>
-    <row r="370" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A370" s="3"/>
-      <c r="B370" s="3"/>
-    </row>
-    <row r="371" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A371" s="3"/>
-      <c r="B371" s="3"/>
-    </row>
-    <row r="372" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A372" s="3"/>
-      <c r="B372" s="3"/>
-    </row>
-    <row r="373" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A373" s="3"/>
-      <c r="B373" s="3"/>
-    </row>
-    <row r="374" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A374" s="3"/>
-      <c r="B374" s="3"/>
-    </row>
-    <row r="375" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A375" s="3"/>
-      <c r="B375" s="3"/>
-    </row>
-    <row r="376" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A376" s="3"/>
-      <c r="B376" s="3"/>
-    </row>
-    <row r="377" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A377" s="3"/>
-      <c r="B377" s="3"/>
-    </row>
-    <row r="378" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A378" s="3"/>
-      <c r="B378" s="3"/>
-    </row>
-    <row r="379" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A379" s="3"/>
-      <c r="B379" s="3"/>
-    </row>
-    <row r="380" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A380" s="3"/>
-      <c r="B380" s="3"/>
-    </row>
-    <row r="381" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A381" s="3"/>
-      <c r="B381" s="3"/>
-    </row>
-    <row r="382" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A382" s="3"/>
-      <c r="B382" s="3"/>
-    </row>
-    <row r="383" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A383" s="3"/>
-      <c r="B383" s="3"/>
-    </row>
-    <row r="384" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A384" s="3"/>
-      <c r="B384" s="3"/>
-    </row>
-    <row r="385" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A385" s="3"/>
-      <c r="B385" s="3"/>
-    </row>
-    <row r="386" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A386" s="3"/>
-      <c r="B386" s="3"/>
-    </row>
-    <row r="387" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A387" s="3"/>
-      <c r="B387" s="3"/>
-    </row>
-    <row r="388" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A388" s="3"/>
-      <c r="B388" s="3"/>
-    </row>
-    <row r="389" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A389" s="3"/>
-      <c r="B389" s="3"/>
-    </row>
-    <row r="390" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A390" s="3"/>
-      <c r="B390" s="3"/>
-    </row>
-    <row r="391" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A391" s="3"/>
-      <c r="B391" s="3"/>
-    </row>
-    <row r="392" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A392" s="3"/>
-      <c r="B392" s="3"/>
-    </row>
-    <row r="393" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A393" s="3"/>
-      <c r="B393" s="3"/>
-    </row>
-    <row r="394" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A394" s="3"/>
-      <c r="B394" s="3"/>
-    </row>
-    <row r="395" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A395" s="3"/>
-      <c r="B395" s="3"/>
-    </row>
-    <row r="396" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A396" s="3"/>
-      <c r="B396" s="3"/>
-    </row>
-    <row r="397" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A397" s="3"/>
-      <c r="B397" s="3"/>
-    </row>
-    <row r="398" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A398" s="3"/>
-      <c r="B398" s="3"/>
-    </row>
-    <row r="399" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A399" s="3"/>
-      <c r="B399" s="3"/>
-    </row>
-    <row r="400" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A400" s="3"/>
-      <c r="B400" s="3"/>
-    </row>
-    <row r="401" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A401" s="3"/>
-      <c r="B401" s="3"/>
-    </row>
-    <row r="402" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A402" s="3"/>
-      <c r="B402" s="3"/>
-    </row>
-    <row r="403" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A403" s="3"/>
-      <c r="B403" s="3"/>
-    </row>
-    <row r="404" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A404" s="3"/>
-      <c r="B404" s="3"/>
-    </row>
-    <row r="405" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A405" s="3"/>
-      <c r="B405" s="3"/>
-    </row>
-    <row r="406" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A406" s="3"/>
-      <c r="B406" s="3"/>
-    </row>
-    <row r="407" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A407" s="3"/>
-      <c r="B407" s="3"/>
-    </row>
-    <row r="408" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A408" s="3"/>
-      <c r="B408" s="3"/>
-    </row>
-    <row r="409" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A409" s="3"/>
-      <c r="B409" s="3"/>
-    </row>
-    <row r="410" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A410" s="3"/>
-      <c r="B410" s="3"/>
-    </row>
-    <row r="411" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A411" s="3"/>
-      <c r="B411" s="3"/>
-    </row>
-    <row r="412" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A412" s="3"/>
-      <c r="B412" s="3"/>
-    </row>
-    <row r="413" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A413" s="3"/>
-      <c r="B413" s="3"/>
-    </row>
-    <row r="414" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A414" s="3"/>
-      <c r="B414" s="3"/>
-    </row>
-    <row r="415" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A415" s="3"/>
-      <c r="B415" s="3"/>
-    </row>
-    <row r="416" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A416" s="3"/>
-      <c r="B416" s="3"/>
-    </row>
-    <row r="417" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A417" s="3"/>
-      <c r="B417" s="3"/>
-    </row>
-    <row r="418" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A418" s="3"/>
-      <c r="B418" s="3"/>
-    </row>
-    <row r="419" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A419" s="3"/>
-      <c r="B419" s="3"/>
-    </row>
-    <row r="420" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A420" s="3"/>
-      <c r="B420" s="3"/>
-    </row>
-    <row r="421" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A421" s="3"/>
-      <c r="B421" s="3"/>
-    </row>
-    <row r="422" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A422" s="3"/>
-      <c r="B422" s="3"/>
-    </row>
-    <row r="423" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A423" s="3"/>
-      <c r="B423" s="3"/>
-    </row>
-    <row r="424" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A424" s="3"/>
-      <c r="B424" s="3"/>
-    </row>
-    <row r="425" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A425" s="3"/>
-      <c r="B425" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A42">
+  <conditionalFormatting sqref="A2:A46">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
